--- a/public/warehouse/location_master.xlsx
+++ b/public/warehouse/location_master.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="46">
   <si>
     <t>WarehouseCode</t>
   </si>
@@ -100,7 +100,7 @@
     <t>TOYS</t>
   </si>
   <si>
-    <t>R9-52-30</t>
+    <t>R1-1-3</t>
   </si>
   <si>
     <t>False</t>
@@ -118,34 +118,40 @@
     <t>HDR</t>
   </si>
   <si>
-    <t>R5-27-10</t>
-  </si>
-  <si>
-    <t>R10-40-10</t>
-  </si>
-  <si>
-    <t>R28-34-60</t>
-  </si>
-  <si>
-    <t>R30-14-50</t>
-  </si>
-  <si>
-    <t>GF103-30-60</t>
+    <t>R1-2-1</t>
+  </si>
+  <si>
+    <t>R1-4-1</t>
+  </si>
+  <si>
+    <t>R1-6-6</t>
+  </si>
+  <si>
+    <t>R4-6-5</t>
+  </si>
+  <si>
+    <t>R4-1-6</t>
   </si>
   <si>
     <t>MTS</t>
   </si>
   <si>
-    <t>GF115-57-50</t>
-  </si>
-  <si>
-    <t>FF140-10-60</t>
-  </si>
-  <si>
-    <t>SF169-62-30</t>
-  </si>
-  <si>
-    <t>TF182-71-40</t>
+    <t>R5-2-5</t>
+  </si>
+  <si>
+    <t>R10-23-6</t>
+  </si>
+  <si>
+    <t>R11-4-3</t>
+  </si>
+  <si>
+    <t>R12-25-4</t>
+  </si>
+  <si>
+    <t>R2-2-5</t>
+  </si>
+  <si>
+    <t>R2-1-2</t>
   </si>
 </sst>
 </file>
@@ -493,7 +499,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main">
   <sheetPr/>
-  <dimension ref="A1:X11"/>
+  <dimension ref="A1:X13"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>
     <row r="1">
@@ -1248,6 +1254,142 @@
       </c>
       <c r="W11" t="s">
         <v>39</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>24</v>
+      </c>
+      <c r="B12" t="s">
+        <v>25</v>
+      </c>
+      <c r="C12" t="s">
+        <v>26</v>
+      </c>
+      <c r="D12" t="s">
+        <v>27</v>
+      </c>
+      <c r="E12" t="s">
+        <v>44</v>
+      </c>
+      <c r="F12">
+        <v>2</v>
+      </c>
+      <c r="G12">
+        <v>2</v>
+      </c>
+      <c r="H12">
+        <v>5</v>
+      </c>
+      <c r="I12">
+        <v>1</v>
+      </c>
+      <c r="J12" t="s">
+        <v>29</v>
+      </c>
+      <c r="L12">
+        <v>1</v>
+      </c>
+      <c r="M12">
+        <v>1200</v>
+      </c>
+      <c r="N12">
+        <v>1000</v>
+      </c>
+      <c r="O12">
+        <v>2000</v>
+      </c>
+      <c r="P12" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q12">
+        <v>1000</v>
+      </c>
+      <c r="R12" t="s">
+        <v>31</v>
+      </c>
+      <c r="S12" t="s">
+        <v>32</v>
+      </c>
+      <c r="T12">
+        <v>10</v>
+      </c>
+      <c r="U12">
+        <v>10</v>
+      </c>
+      <c r="V12">
+        <v>10</v>
+      </c>
+      <c r="W12" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>24</v>
+      </c>
+      <c r="B13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13" t="s">
+        <v>26</v>
+      </c>
+      <c r="D13" t="s">
+        <v>27</v>
+      </c>
+      <c r="E13" t="s">
+        <v>45</v>
+      </c>
+      <c r="F13">
+        <v>2</v>
+      </c>
+      <c r="G13">
+        <v>1</v>
+      </c>
+      <c r="H13">
+        <v>2</v>
+      </c>
+      <c r="I13">
+        <v>1</v>
+      </c>
+      <c r="J13" t="s">
+        <v>29</v>
+      </c>
+      <c r="L13">
+        <v>1</v>
+      </c>
+      <c r="M13">
+        <v>1200</v>
+      </c>
+      <c r="N13">
+        <v>1000</v>
+      </c>
+      <c r="O13">
+        <v>2000</v>
+      </c>
+      <c r="P13" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q13">
+        <v>1000</v>
+      </c>
+      <c r="R13" t="s">
+        <v>31</v>
+      </c>
+      <c r="S13" t="s">
+        <v>32</v>
+      </c>
+      <c r="T13">
+        <v>10</v>
+      </c>
+      <c r="U13">
+        <v>10</v>
+      </c>
+      <c r="V13">
+        <v>10</v>
+      </c>
+      <c r="W13" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>
